--- a/output/graficos_dimensiones/comunal_e_prebrut_a_2020_magallanes.xlsx
+++ b/output/graficos_dimensiones/comunal_e_prebrut_a_2020_magallanes.xlsx
@@ -60,12 +60,12 @@
     <t xml:space="preserve">San Gregorio</t>
   </si>
   <si>
+    <t xml:space="preserve">Timaukel</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cabo de Hornos</t>
   </si>
   <si>
-    <t xml:space="preserve">Timaukel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:14</t>
+    <t xml:space="preserve">2026-09-10 00:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -633,7 +633,7 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>12201</v>
+        <v>12303</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -646,7 +646,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>12303</v>
+        <v>12201</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>

--- a/output/graficos_dimensiones/comunal_e_prebrut_a_2020_magallanes.xlsx
+++ b/output/graficos_dimensiones/comunal_e_prebrut_a_2020_magallanes.xlsx
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:19</t>
+    <t xml:space="preserve">2026-09-18 10:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
